--- a/experiments/E6_model_versions/results/results.xlsx
+++ b/experiments/E6_model_versions/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolov5n</t>
+          <t>yolov8n</t>
         </is>
       </c>
     </row>
@@ -575,15 +575,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -672,55 +672,55 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolov5n</t>
+          <t>yolov8n</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolov5nu</t>
+          <t>yolov8n</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>640</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4430999483477777</v>
+        <v>0.4590884378625956</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2335836794159872</v>
+        <v>0.2428204892375275</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5279445337386338</v>
+        <v>0.5326084225452772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4316343314252292</v>
+        <v>0.4445608135825527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3450823302744565</v>
+        <v>0.3697887679022301</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3611692677967097</v>
+        <v>0.4082122841993413</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4859218868073069</v>
+        <v>0.4894189087191429</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5802263085126377</v>
+        <v>0.5689337906296679</v>
       </c>
       <c r="L2" t="n">
-        <v>2.636348</v>
+        <v>3.138732</v>
       </c>
       <c r="M2" t="n">
-        <v>5.524482</v>
+        <v>6.502826</v>
       </c>
       <c r="N2" t="n">
-        <v>117.2657007334237</v>
+        <v>132.963032299934</v>
       </c>
       <c r="O2" t="n">
-        <v>110.9515732000242</v>
+        <v>127.179803733361</v>
       </c>
       <c r="P2" t="n">
-        <v>3.778598051915131</v>
+        <v>3.452752467520428</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E6_model_versions/results/results.xlsx
+++ b/experiments/E6_model_versions/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolov8n</t>
+          <t>yolov10n</t>
         </is>
       </c>
     </row>
@@ -574,15 +574,15 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -672,55 +672,55 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolov8n</t>
+          <t>yolov10n</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolov8n</t>
+          <t>yolov10n</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>640</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4590884378625956</v>
+        <v>0.4790572175452031</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2428204892375275</v>
+        <v>0.2637606541375242</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5326084225452772</v>
+        <v>0.5503488029865988</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4445608135825527</v>
+        <v>0.4621241464078122</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3697887679022301</v>
+        <v>0.3776528305123846</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4082122841993413</v>
+        <v>0.4124997625737669</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4894189087191429</v>
+        <v>0.5129299503446353</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5689337906296679</v>
+        <v>0.6131463267500254</v>
       </c>
       <c r="L2" t="n">
-        <v>3.138732</v>
+        <v>2.738584</v>
       </c>
       <c r="M2" t="n">
-        <v>6.502826</v>
+        <v>5.815674</v>
       </c>
       <c r="N2" t="n">
-        <v>132.963032299934</v>
+        <v>127.2730074999648</v>
       </c>
       <c r="O2" t="n">
-        <v>127.179803733361</v>
+        <v>121.4112006667165</v>
       </c>
       <c r="P2" t="n">
-        <v>3.452752467520428</v>
+        <v>3.764012707449658</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E6_model_versions/results/results.xlsx
+++ b/experiments/E6_model_versions/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolov10n</t>
+          <t>yolo11n</t>
         </is>
       </c>
     </row>
@@ -574,16 +574,16 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -672,55 +672,55 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolov10n</t>
+          <t>yolo11n</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolov10n</t>
+          <t>yolo11n</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>640</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4790572175452031</v>
+        <v>0.4815996110476966</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2637606541375242</v>
+        <v>0.2600287397964783</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5503488029865988</v>
+        <v>0.55761400346134</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4621241464078122</v>
+        <v>0.4586332447745491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3776528305123846</v>
+        <v>0.387682778448116</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4124997625737669</v>
+        <v>0.4140608304758108</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5129299503446353</v>
+        <v>0.510089308625239</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6131463267500254</v>
+        <v>0.6145655266416206</v>
       </c>
       <c r="L2" t="n">
-        <v>2.738584</v>
+        <v>2.605612</v>
       </c>
       <c r="M2" t="n">
-        <v>5.815674</v>
+        <v>5.501914</v>
       </c>
       <c r="N2" t="n">
-        <v>127.2730074999648</v>
+        <v>131.1351556333042</v>
       </c>
       <c r="O2" t="n">
-        <v>121.4112006667165</v>
+        <v>125.1787125666851</v>
       </c>
       <c r="P2" t="n">
-        <v>3.764012707449658</v>
+        <v>3.6725438630233</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E6_model_versions/results/results.xlsx
+++ b/experiments/E6_model_versions/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolo11n</t>
+          <t>yolo26n</t>
         </is>
       </c>
     </row>
@@ -579,16 +579,16 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -672,55 +672,55 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolo11n</t>
+          <t>yolo26n</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolo11n</t>
+          <t>yolo26n</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>640</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4815996110476966</v>
+        <v>0.5231161428943761</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2600287397964783</v>
+        <v>0.2933595902066846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.55761400346134</v>
+        <v>0.6024861031864486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4586332447745491</v>
+        <v>0.4832042353781484</v>
       </c>
       <c r="H2" t="n">
-        <v>0.387682778448116</v>
+        <v>0.4421199475185175</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4140608304758108</v>
+        <v>0.449452608898985</v>
       </c>
       <c r="J2" t="n">
-        <v>0.510089308625239</v>
+        <v>0.5410165026563789</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6145655266416206</v>
+        <v>0.6598755125036231</v>
       </c>
       <c r="L2" t="n">
-        <v>2.605612</v>
+        <v>2.535344</v>
       </c>
       <c r="M2" t="n">
-        <v>5.501914</v>
+        <v>5.449989</v>
       </c>
       <c r="N2" t="n">
-        <v>131.1351556333042</v>
+        <v>117.181698133633</v>
       </c>
       <c r="O2" t="n">
-        <v>125.1787125666851</v>
+        <v>111.1906334335193</v>
       </c>
       <c r="P2" t="n">
-        <v>3.6725438630233</v>
+        <v>4.464145435900912</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E6_model_versions/results/results.xlsx
+++ b/experiments/E6_model_versions/results/results.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolo26n</t>
+          <t>yolov5n,yolov8n,yolov10n,yolo11n,yolo26n</t>
         </is>
       </c>
     </row>
@@ -571,24 +571,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -672,55 +672,271 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolo26n</t>
+          <t>yolov5n</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolo26n</t>
+          <t>yolov5nu</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>640</v>
       </c>
       <c r="D2" t="n">
+        <v>0.4430999483477777</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2335836794159872</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5279445337386338</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4316343314252292</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3450823302744565</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3611692677967097</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4859218868073069</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5802263085126377</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.636348</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.524482</v>
+      </c>
+      <c r="N2" t="n">
+        <v>124.0348049671108</v>
+      </c>
+      <c r="O2" t="n">
+        <v>117.8488848003326</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.57238396484979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>yolov8n</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>yolov8n</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>640</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4590884378625956</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2428204892375275</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5326084225452772</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4445608135825527</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3697887679022301</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4082122841993413</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4894189087191429</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5689337906296679</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.138732</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.502826</v>
+      </c>
+      <c r="N3" t="n">
+        <v>136.6679068000546</v>
+      </c>
+      <c r="O3" t="n">
+        <v>130.8400401666707</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.359153210228374</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>yolov10n</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>yolov10n</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>640</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4790572175452031</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2637606541375242</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5503488029865988</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4621241464078122</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3776528305123846</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4124997625737669</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5129299503446353</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6131463267500254</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.738584</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5.815674</v>
+      </c>
+      <c r="N4" t="n">
+        <v>129.4576570664503</v>
+      </c>
+      <c r="O4" t="n">
+        <v>123.2883333998567</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.700493492627508</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>yolo11n</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>yolo11n</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>640</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4815996110476966</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2600287397964783</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.55761400346134</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4586332447745491</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.387682778448116</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4140608304758108</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.510089308625239</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.6145655266416206</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.605612</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.501914</v>
+      </c>
+      <c r="N5" t="n">
+        <v>144.837647300119</v>
+      </c>
+      <c r="O5" t="n">
+        <v>137.0321566001318</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.325099654855419</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>yolo26n</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yolo26n</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>640</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.5231161428943761</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E6" t="n">
         <v>0.2933595902066846</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F6" t="n">
         <v>0.6024861031864486</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G6" t="n">
         <v>0.4832042353781484</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H6" t="n">
         <v>0.4421199475185175</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I6" t="n">
         <v>0.449452608898985</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J6" t="n">
         <v>0.5410165026563789</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K6" t="n">
         <v>0.6598755125036231</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L6" t="n">
         <v>2.535344</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M6" t="n">
         <v>5.449989</v>
       </c>
-      <c r="N2" t="n">
-        <v>117.181698133633</v>
-      </c>
-      <c r="O2" t="n">
-        <v>111.1906334335193</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4.464145435900912</v>
+      <c r="N6" t="n">
+        <v>137.3144962334967</v>
+      </c>
+      <c r="O6" t="n">
+        <v>129.2208822333729</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.80962066819837</v>
       </c>
     </row>
   </sheetData>
